--- a/DownloadTodosResultadosLoterias/downloads/RepresentacaoNoVoantes.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/RepresentacaoNoVoantes.xlsx
@@ -5,30 +5,44 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcio Fernando Maia\Desktop\Ajustando\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Loterias\LoteriasPosicao\DownloadTodosResultadosLoterias\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EABB93EC-2DED-4B51-AC68-89398C398EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8CE053-C47C-4F72-A34D-DB252B819278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2410" yWindow="2250" windowWidth="21600" windowHeight="10500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" firstSheet="3" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="diadesorte" sheetId="1" r:id="rId1"/>
     <sheet name="lotofacil" sheetId="2" r:id="rId2"/>
-    <sheet name="megasena" sheetId="3" r:id="rId3"/>
-    <sheet name="duplasena" sheetId="4" r:id="rId4"/>
-    <sheet name="maismilionaria" sheetId="5" r:id="rId5"/>
-    <sheet name="timemania" sheetId="6" r:id="rId6"/>
-    <sheet name="lotomania" sheetId="7" r:id="rId7"/>
-    <sheet name="quina" sheetId="9" r:id="rId8"/>
-    <sheet name="supersete" sheetId="10" r:id="rId9"/>
+    <sheet name="Planilha1" sheetId="11" r:id="rId3"/>
+    <sheet name="megasena" sheetId="3" r:id="rId4"/>
+    <sheet name="duplasena" sheetId="4" r:id="rId5"/>
+    <sheet name="maismilionaria" sheetId="5" r:id="rId6"/>
+    <sheet name="timemania" sheetId="6" r:id="rId7"/>
+    <sheet name="lotomania" sheetId="7" r:id="rId8"/>
+    <sheet name="quina" sheetId="9" r:id="rId9"/>
+    <sheet name="supersete" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="166">
   <si>
     <t>Intervalo histórico por posição (números ordenados de cada concurso)</t>
   </si>
@@ -460,13 +474,79 @@
   </si>
   <si>
     <t>Concursos válidos: 802</t>
+  </si>
+  <si>
+    <t>Modalidade</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>O que atualiza ao vivo</t>
+  </si>
+  <si>
+    <t>Dia de Sorte</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>7 dezenas + mês</t>
+  </si>
+  <si>
+    <t>Lotofácil</t>
+  </si>
+  <si>
+    <t>15 dezenas</t>
+  </si>
+  <si>
+    <t>Quina</t>
+  </si>
+  <si>
+    <t>5 dezenas</t>
+  </si>
+  <si>
+    <t>Mega-Sena</t>
+  </si>
+  <si>
+    <t>6 dezenas</t>
+  </si>
+  <si>
+    <t>Lotomania</t>
+  </si>
+  <si>
+    <t>50 dezenas</t>
+  </si>
+  <si>
+    <t>Timemania</t>
+  </si>
+  <si>
+    <t>10 dezenas + time</t>
+  </si>
+  <si>
+    <t>Dupla Sena</t>
+  </si>
+  <si>
+    <t>6 dezenas (1º sorteio)</t>
+  </si>
+  <si>
+    <t>6 dezenas + 2 trevos</t>
+  </si>
+  <si>
+    <t>Super Sete</t>
+  </si>
+  <si>
+    <t>7 colunas</t>
+  </si>
+  <si>
+    <t>+Milionária</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -515,8 +595,20 @@
       <sz val="8"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFF0F0F0"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFF0F0F0"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -542,6 +634,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF141414"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -572,7 +670,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -625,20 +723,26 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -986,27 +1090,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="11" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23">
+      <c r="A1" s="20">
         <v>1</v>
       </c>
       <c r="B1" s="26"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
       <c r="O1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
     </row>
     <row r="2" spans="1:18" ht="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -1022,12 +1126,12 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
-      <c r="O2" s="22" t="s">
+      <c r="O2" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
@@ -1106,12 +1210,12 @@
       <c r="M4" s="9">
         <v>20</v>
       </c>
-      <c r="O4" s="20" t="s">
+      <c r="O4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -1151,12 +1255,12 @@
       <c r="M5" s="9">
         <v>30</v>
       </c>
-      <c r="O5" s="22" t="s">
+      <c r="O5" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
@@ -1340,20 +1444,20 @@
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="O15" s="20" t="s">
+      <c r="O15" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="O16" s="22" t="s">
+      <c r="O16" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="P16" s="21"/>
-      <c r="Q16" s="21"/>
-      <c r="R16" s="21"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
     </row>
     <row r="17" spans="15:18" x14ac:dyDescent="0.35">
       <c r="O17" s="15" t="s">
@@ -1394,6 +1498,172 @@
     <mergeCell ref="O1:R1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="4" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="14"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="17">
+        <v>0</v>
+      </c>
+      <c r="D9" s="17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="19">
+        <v>0</v>
+      </c>
+      <c r="D10" s="19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11" s="17">
+        <v>0</v>
+      </c>
+      <c r="D11" s="17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="19">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="17">
+        <v>0</v>
+      </c>
+      <c r="D13" s="17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" s="19">
+        <v>0</v>
+      </c>
+      <c r="D14" s="19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="17">
+        <v>0</v>
+      </c>
+      <c r="D15" s="17">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1412,19 +1682,19 @@
     <row r="1" spans="1:13" ht="11" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
-      <c r="D1" s="23">
+      <c r="D1" s="20">
         <v>1</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
       <c r="J1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
     </row>
     <row r="2" spans="1:13" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -1435,12 +1705,12 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
@@ -1489,12 +1759,12 @@
       <c r="H4" s="9">
         <v>10</v>
       </c>
-      <c r="J4" s="20" t="s">
+      <c r="J4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -1519,12 +1789,12 @@
       <c r="H5" s="9">
         <v>15</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
@@ -1808,6 +2078,129 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B129663A-5EA6-4688-A7D7-2F0FA6CBE82D}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="20.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="23" x14ac:dyDescent="0.35">
+      <c r="A2" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="23" x14ac:dyDescent="0.35">
+      <c r="A7" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="23" x14ac:dyDescent="0.35">
+      <c r="A8" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="23" x14ac:dyDescent="0.35">
+      <c r="A9" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>164</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1823,24 +2216,24 @@
     <row r="1" spans="1:18" ht="11" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
-      <c r="D1" s="23">
+      <c r="D1" s="20">
         <v>1</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
       <c r="O1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
     </row>
     <row r="2" spans="1:18" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -1856,12 +2249,12 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
-      <c r="O2" s="22" t="s">
+      <c r="O2" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
@@ -1940,12 +2333,12 @@
       <c r="M4" s="9">
         <v>20</v>
       </c>
-      <c r="O4" s="20" t="s">
+      <c r="O4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -1985,12 +2378,12 @@
       <c r="M5" s="9">
         <v>30</v>
       </c>
-      <c r="O5" s="22" t="s">
+      <c r="O5" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
@@ -2213,7 +2606,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:R32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2229,24 +2622,24 @@
     <row r="1" spans="1:18" ht="11" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
-      <c r="D1" s="23">
+      <c r="D1" s="20">
         <v>1</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
       <c r="O1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
     </row>
     <row r="2" spans="1:18" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -2262,12 +2655,12 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
-      <c r="O2" s="22" t="s">
+      <c r="O2" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
@@ -2346,12 +2739,12 @@
       <c r="M4" s="9">
         <v>20</v>
       </c>
-      <c r="O4" s="20" t="s">
+      <c r="O4" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -2391,12 +2784,12 @@
       <c r="M5" s="9">
         <v>30</v>
       </c>
-      <c r="O5" s="22" t="s">
+      <c r="O5" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
@@ -2571,20 +2964,20 @@
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="O14" s="20" t="s">
+      <c r="O14" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="21"/>
-      <c r="R14" s="21"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="O15" s="22" t="s">
+      <c r="O15" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="O16" s="15" t="s">
@@ -2685,20 +3078,20 @@
       </c>
     </row>
     <row r="24" spans="15:18" x14ac:dyDescent="0.35">
-      <c r="O24" s="20" t="s">
+      <c r="O24" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="21"/>
-      <c r="R24" s="21"/>
+      <c r="P24" s="23"/>
+      <c r="Q24" s="23"/>
+      <c r="R24" s="23"/>
     </row>
     <row r="25" spans="15:18" x14ac:dyDescent="0.35">
-      <c r="O25" s="22" t="s">
+      <c r="O25" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
+      <c r="P25" s="23"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="23"/>
     </row>
     <row r="26" spans="15:18" x14ac:dyDescent="0.35">
       <c r="O26" s="15" t="s">
@@ -2814,7 +3207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2830,19 +3223,19 @@
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
-      <c r="D1" s="23">
+      <c r="D1" s="20">
         <v>1</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
       <c r="J1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
     </row>
     <row r="2" spans="1:13" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -2853,12 +3246,12 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
@@ -2907,12 +3300,12 @@
       <c r="H4" s="9">
         <v>10</v>
       </c>
-      <c r="J4" s="20" t="s">
+      <c r="J4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
@@ -2937,12 +3330,12 @@
       <c r="H5" s="9">
         <v>15</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
@@ -3214,12 +3607,12 @@
       <c r="F14" s="9">
         <v>3</v>
       </c>
-      <c r="J14" s="20" t="s">
+      <c r="J14" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D15" s="9">
@@ -3231,12 +3624,12 @@
       <c r="F15" s="9">
         <v>6</v>
       </c>
-      <c r="J15" s="22" t="s">
+      <c r="J15" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="J16" s="15" t="s">
@@ -3294,7 +3687,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3310,24 +3703,24 @@
     <row r="1" spans="1:18" ht="11" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
-      <c r="D1" s="23">
+      <c r="D1" s="20">
         <v>1</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
       <c r="O1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
     </row>
     <row r="2" spans="1:18" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -3343,12 +3736,12 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
-      <c r="O2" s="22" t="s">
+      <c r="O2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
@@ -3427,12 +3820,12 @@
       <c r="M4" s="9">
         <v>20</v>
       </c>
-      <c r="O4" s="20" t="s">
+      <c r="O4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -3472,12 +3865,12 @@
       <c r="M5" s="9">
         <v>30</v>
       </c>
-      <c r="O5" s="22" t="s">
+      <c r="O5" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
@@ -3727,7 +4120,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3741,27 +4134,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="11" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23">
+      <c r="A1" s="20">
         <v>1</v>
       </c>
       <c r="B1" s="26"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
       <c r="O1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
     </row>
     <row r="2" spans="1:18" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
@@ -3777,12 +4170,12 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
-      <c r="O2" s="22" t="s">
+      <c r="O2" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
@@ -3861,12 +4254,12 @@
       <c r="M4" s="9">
         <v>20</v>
       </c>
-      <c r="O4" s="20" t="s">
+      <c r="O4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -3906,12 +4299,12 @@
       <c r="M5" s="9">
         <v>30</v>
       </c>
-      <c r="O5" s="22" t="s">
+      <c r="O5" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
@@ -4330,7 +4723,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4345,33 +4738,33 @@
       <c r="A3" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
@@ -4455,172 +4848,6 @@
       </c>
       <c r="D13" s="17">
         <v>80</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A6:D6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="4" width="13" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="14"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="C9" s="17">
-        <v>0</v>
-      </c>
-      <c r="D9" s="17">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" s="19">
-        <v>0</v>
-      </c>
-      <c r="D10" s="19">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="C11" s="17">
-        <v>0</v>
-      </c>
-      <c r="D11" s="17">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" s="19">
-        <v>0</v>
-      </c>
-      <c r="D12" s="19">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="C13" s="17">
-        <v>0</v>
-      </c>
-      <c r="D13" s="17">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="C14" s="19">
-        <v>0</v>
-      </c>
-      <c r="D14" s="19">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="17">
-        <v>0</v>
-      </c>
-      <c r="D15" s="17">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
